--- a/source/data/прайс-проверить-друзьям.xlsx
+++ b/source/data/прайс-проверить-друзьям.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -559,91 +559,91 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Замена технологических жидкостей с промывкой</t>
+          <t>Замена масла в АКПП</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Замена масла и технических жидкостей</t>
+          <t>Замена масла в автоматической коробке</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>цена скопирована у конкурента — проверить</t>
+          <t>проверить: делаете ли вы это?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Замена масла на всех марках и моделях, тормозная система, система охлаждения, ходовая часть, плановое ТО.</t>
+          <t>Частичная или полная замена с фильтром и очисткой поддона. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Замена тормозных колодок</t>
+          <t>Замена сцепления</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ремонт тормозной системы, замена колодок</t>
+          <t>Замена комплекта сцепления</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>цена скопирована у конкурента — проверить</t>
+          <t>проверить: делаете ли вы это?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Замена дисков и колодок, чистка и смазка направляющих, обслуживание суппортов.</t>
+          <t>Замена диска, корзины и выжимного, осмотр маховика. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Потерял ключ от машины</t>
+          <t>Замена технологических жидкостей с промывкой</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Восстановление ключей при полной утере</t>
+          <t>Замена масла и технических жидкостей</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>проверить: делаете ли вы это?</t>
+          <t>цена скопирована у конкурента — проверить</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Изготовление нового ключа, когда потеряны все. Работаем с большинством популярных марок. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена масла на всех марках и моделях, тормозная система, система охлаждения, ходовая часть, плановое ТО.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Предпродажная диагностика</t>
+          <t>Замена тормозных колодок</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Предпродажная диагностика</t>
+          <t>Ремонт тормозной системы, замена колодок</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -652,19 +652,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Проверка автомобиля перед покупкой: толщиномер по кузову, сканер по всем блокам, осмотр на подъёмнике.</t>
+          <t>Замена дисков и колодок, чистка и смазка направляющих, обслуживание суппортов.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Привязка ключа к машине</t>
+          <t>Потерял ключ от машины</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Программирование автомобильных ключей</t>
+          <t>Восстановление ключей при полной утере</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -677,98 +677,98 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Привязка новых ключей к автомобилю, программирование чипов, настройка штатных систем доступа. Актуальную стоимость уточните по телефону.</t>
+          <t>Изготовление нового ключа, когда потеряны все. Работаем с большинством популярных марок. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ремонт авто Красногорск</t>
+          <t>Предпродажная диагностика</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ремонт турбин</t>
+          <t>Предпродажная диагностика</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>проверить: делаете ли вы это?</t>
+          <t>цена скопирована у конкурента — проверить</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Диагностика турбокомпрессора, ремонт или замена узла. Актуальную стоимость уточните по телефону.</t>
+          <t>Проверка автомобиля перед покупкой: толщиномер по кузову, сканер по всем блокам, осмотр на подъёмнике.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ремонт автомобильного отопителя (печки)</t>
+          <t>Привязка ключа к машине</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ремонт печки и замена радиатора отопителя</t>
+          <t>Программирование автомобильных ключей</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>цена скопирована у конкурента — проверить</t>
+          <t>проверить: делаете ли вы это?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Устраняем причину, по которой в салоне не греет: радиатор отопителя, краны, воздушные пробки.</t>
+          <t>Привязка новых ключей к автомобилю, программирование чипов, настройка штатных систем доступа. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ремонт иномарок</t>
+          <t>Ремонт авто Красногорск</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ремонт двигателей</t>
+          <t>Ремонт турбин</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>цена скопирована у конкурента — проверить</t>
+          <t>проверить: делаете ли вы это?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Капитальный и частичный ремонт двигателей любой сложности.</t>
+          <t>Диагностика турбокомпрессора, ремонт или замена узла. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ремонт кондиционера</t>
+          <t>Ремонт автомобильного отопителя (печки)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Заправка и ремонт кондиционера</t>
+          <t>Ремонт печки и замена радиатора отопителя</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -777,19 +777,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Диагностика и поиск утечек, вакуумирование, заправка фреоном R134a, проверка на герметичность. Ремонт и замена компрессора, муфты, конденсатора, клапанов. Промывка системы.</t>
+          <t>Устраняем причину, по которой в салоне не греет: радиатор отопителя, краны, воздушные пробки.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ремонт стартеров и генераторов</t>
+          <t>Ремонт иномарок</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ремонт стартеров и генераторов</t>
+          <t>Ремонт двигателей</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -802,94 +802,94 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Диагностика неисправности, ремонт стартеров и генераторов, замена щёток и подшипников. Возможен обмен на восстановленный. Запчасти в наличии, гарантия на работу.</t>
+          <t>Капитальный и частичный ремонт двигателей любой сложности.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>СТО Красногорск</t>
+          <t>Ремонт кондиционера</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Замена масла в переднем редукторе</t>
+          <t>Заправка и ремонт кондиционера</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>проверить: делаете ли вы это?</t>
+          <t>цена скопирована у конкурента — проверить</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Замена трансмиссионного масла, проверка сальников на течь. Актуальную стоимость уточните по телефону.</t>
+          <t>Диагностика и поиск утечек, вакуумирование, заправка фреоном R134a, проверка на герметичность. Ремонт и замена компрессора, муфты, конденсатора, клапанов. Промывка системы.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Сколько стоит ремонт авто</t>
+          <t>Ремонт стартеров и генераторов</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Замена масла в заднем редукторе</t>
+          <t>Ремонт стартеров и генераторов</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>проверить: делаете ли вы это?</t>
+          <t>цена скопирована у конкурента — проверить</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Замена трансмиссионного масла в редукторе, осмотр сальников. Актуальную стоимость уточните по телефону.</t>
+          <t>Диагностика неисправности, ремонт стартеров и генераторов, замена щёток и подшипников. Возможен обмен на восстановленный. Запчасти в наличии, гарантия на работу.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Слесарные работы</t>
+          <t>СТО Красногорск</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ремонт подвески и замена масел</t>
+          <t>Замена масла в переднем редукторе</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>цена скопирована у конкурента — проверить</t>
+          <t>проверить: делаете ли вы это?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ремонт подвески, замена колодок, плановое техническое обслуживание.</t>
+          <t>Замена трансмиссионного масла, проверка сальников на течь. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Техническое обслуживание авто</t>
+          <t>Сколько стоит ремонт авто</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ремонт головки блока цилиндров</t>
+          <t>Замена масла в заднем редукторе</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -902,23 +902,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Снятие, опрессовка, шлифовка плоскости, замена маслосъёмных колпачков. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена трансмиссионного масла в редукторе, осмотр сальников. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Установка дополнительного оборудования</t>
+          <t>Слесарные работы</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Установка дополнительного оборудования</t>
+          <t>Ремонт подвески и замена масел</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -927,48 +927,48 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ДХО наружные и в секцию поворота, видеорегистраторы, парктроники, защитные сетки радиатора, дополнительное освещение. По другим работам звоните.</t>
+          <t>Ремонт подвески, замена колодок, плановое техническое обслуживание.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Чип-тюнинг</t>
+          <t>Техническое обслуживание авто</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Чип-тюнинг</t>
+          <t>Ремонт головки блока цилиндров</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>цена скопирована у конкурента — проверить</t>
+          <t>проверить: делаете ли вы это?</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Профессиональный чип-тюнинг: Stage 1, 2, 3, отключение DPF, EGR, AdBlue, катализатора. Перед прошивкой обязательная компьютерная диагностика.</t>
+          <t>Снятие, опрессовка, шлифовка плоскости, замена маслосъёмных колпачков. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Шиномонтаж R13-R20</t>
+          <t>Установка дополнительного оборудования</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Шиномонтаж</t>
+          <t>Установка дополнительного оборудования</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -977,23 +977,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Легковой шиномонтаж R13–R20: снятие, перебортовка, балансировка, установка.</t>
+          <t>ДХО наружные и в секцию поворота, видеорегистраторы, парктроники, защитные сетки радиатора, дополнительное освещение. По другим работам звоните.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Эндоскопия двигателя</t>
+          <t>Чип-тюнинг</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Проверка цилиндров эндоскопом</t>
+          <t>Чип-тюнинг</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1002,61 +1002,69 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Проверка бензиновых и дизельных двигателей без разборки: задиры и ржавчина на стенках цилиндров, нагар и отложения во впускном и выпускном каналах.</t>
+          <t>Профессиональный чип-тюнинг: Stage 1, 2, 3, отключение DPF, EGR, AdBlue, катализатора. Перед прошивкой обязательная компьютерная диагностика.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Шиномонтаж R13-R20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Чип-тюнинг Stage 1</t>
+          <t>Шиномонтаж</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>1500</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>цена скопирована у конкурента — проверить</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Безопасное увеличение мощности без механических доработок двигателя. Актуальную стоимость уточните по телефону.</t>
+          <t>Легковой шиномонтаж R13–R20: снятие, перебортовка, балансировка, установка.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Автосервис Красногорск</t>
+          <t>Эндоскопия двигателя</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Замена водяного насоса (помпы)</t>
+          <t>Проверка цилиндров эндоскопом</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>1500</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>цена скопирована у конкурента — проверить</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Замена помпы со сливом и заливкой антифриза, проверка системы на утечки. Актуальную стоимость уточните по телефону.</t>
+          <t>Проверка бензиновых и дизельных двигателей без разборки: задиры и ржавчина на стенках цилиндров, нагар и отложения во впускном и выпускном каналах.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Автосервис Красногорск</t>
+          <t>Stage 1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ремонт выхлопной системы</t>
+          <t>Чип-тюнинг Stage 1</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1065,19 +1073,19 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Сварка и замена элементов выхлопа: гофра, резонатор, банка, крепления. Актуальную стоимость уточните по телефону.</t>
+          <t>Безопасное увеличение мощности без механических доработок двигателя. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Автосервис Москва</t>
+          <t>Stage 2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Замена приёмной трубы глушителя</t>
+          <t>Чип-тюнинг Stage 2</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1086,19 +1094,19 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Замена приёмной трубы и прокладок, устранение прогара и посторонних звуков. Актуальную стоимость уточните по телефону.</t>
+          <t>Настройка под доработанный выпуск и впуск. Делаем после замера на месте. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Автосервис Москва</t>
+          <t>Автосервис Волоколамское шоссе</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Замена прокладки приёмной трубы</t>
+          <t>Ремонт ходовой части</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1107,19 +1115,19 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Замена прокладки на стыке выпускного коллектора и приёмной трубы. Актуальную стоимость уточните по телефону.</t>
+          <t>Рычаги, стойки, сайлентблоки, шаровые — со сметой до начала работ. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Автосервис Мякинино</t>
+          <t>Автосервис Красногорск</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Замена натяжителя приводного ремня</t>
+          <t>Замена водяного насоса (помпы)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1128,19 +1136,19 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Замена натяжителя и роликов, проверка состояния ремня. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена помпы со сливом и заливкой антифриза, проверка системы на утечки. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Автосервис Мякинино</t>
+          <t>Автосервис Красногорск</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Диагностика двигателя</t>
+          <t>Ремонт выхлопной системы</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1149,19 +1157,19 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Проверка работы двигателя по сканеру и на слух, поиск причины перебоев. Актуальную стоимость уточните по телефону.</t>
+          <t>Сварка и замена элементов выхлопа: гофра, резонатор, банка, крепления. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Автосервис Павшинская пойма</t>
+          <t>Автосервис Митино</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Замена термостата</t>
+          <t>Ремонт глушителя</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1170,19 +1178,19 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Замена термостата, доливка антифриза, проверка выхода на рабочую температуру. Актуальную стоимость уточните по телефону.</t>
+          <t>Устранение прогара и гула, аргонная сварка. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Автосервис Павшинская пойма</t>
+          <t>Автосервис Митино</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ремонт системы охлаждения двигателя</t>
+          <t>Диагностика подвески</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1191,19 +1199,19 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Поиск утечек, замена радиатора, патрубков и термостата. Актуальную стоимость уточните по телефону.</t>
+          <t>Осмотр на подъёмнике, показываем каждый люфт руками. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Автосервис отзывы</t>
+          <t>Автосервис Москва</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Замена ступицы</t>
+          <t>Замена приёмной трубы глушителя</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1212,19 +1220,19 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Замена ступичного узла или подшипника, проверка второй стороны. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена приёмной трубы и прокладок, устранение прогара и посторонних звуков. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Автосервис рядом</t>
+          <t>Автосервис Москва</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Замена бензонасоса</t>
+          <t>Замена прокладки приёмной трубы</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1233,19 +1241,19 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Снятие лючка или бака, замена насоса, проверка производительности. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена прокладки на стыке выпускного коллектора и приёмной трубы. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Автосервис рядом со мной</t>
+          <t>Автосервис Мякинино</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Переклейка поддона двигателя</t>
+          <t>Замена натяжителя приводного ремня</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1254,19 +1262,19 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Снятие поддона, очистка привалочных плоскостей, герметизация. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена натяжителя и роликов, проверка состояния ремня. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Автосервис с гарантией</t>
+          <t>Автосервис Мякинино</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Замена опоры амортизатора</t>
+          <t>Диагностика двигателя</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1275,19 +1283,19 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Замена опор и опорных подшипников, осмотр пружин и пыльников. Актуальную стоимость уточните по телефону.</t>
+          <t>Проверка работы двигателя по сканеру и на слух, поиск причины перебоев. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Автосервис улица Жуковского</t>
+          <t>Автосервис Нахабино</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Замена топливного фильтра</t>
+          <t>Замена масла и фильтров</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1296,19 +1304,19 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Замена фильтра тонкой очистки, проверка давления в топливной рампе. Актуальную стоимость уточните по телефону.</t>
+          <t>Плановое обслуживание: масло, фильтры, осмотр по регламенту. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Автосервис улица Жуковского</t>
+          <t>Автосервис Нахабино</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Замена антифриза</t>
+          <t>Удаление катализатора</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1317,19 +1325,19 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Полная замена охлаждающей жидкости с промывкой системы. Актуальную стоимость уточните по телефону.</t>
+          <t>Удаление с установкой пламегасителя и корректной прошивкой. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Адаптация ЭБУ</t>
+          <t>Автосервис Опалиха</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Отключение ошибок и адаптация блоков управления</t>
+          <t>Компьютерная диагностика автомобиля</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1338,19 +1346,19 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Настройка электронных систем и адаптация блоков после ремонта, устранение программных ошибок. Актуальную стоимость уточните по телефону.</t>
+          <t>Полная диагностика по всем блокам, разбор причины простыми словами. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Диагностика Авто Москва</t>
+          <t>Автосервис Опалиха</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Комплексная диагностика</t>
+          <t>Ремонт выхлопной системы</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1359,19 +1367,19 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Двигатель, электрика, подвеска и тормоза по одному чек-листу. Актуальную стоимость уточните по телефону.</t>
+          <t>Сварка, замена гофры, резонатора и банки глушителя. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Диагностика автомобиля Москва</t>
+          <t>Автосервис Павшинская пойма</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Замена прокладки клапанной крышки</t>
+          <t>Замена термостата</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1380,19 +1388,19 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Замена прокладки, устранение запотевания и течи масла. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена термостата, доливка антифриза, проверка выхода на рабочую температуру. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Диагностика автомобиля Москва</t>
+          <t>Автосервис Павшинская пойма</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Промывка двигателя</t>
+          <t>Ремонт системы охлаждения двигателя</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1401,19 +1409,19 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Мягкая промывка масляной системы при замене масла. Актуальную стоимость уточните по телефону.</t>
+          <t>Поиск утечек, замена радиатора, патрубков и термостата. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Диагностика выхлопа Москва</t>
+          <t>Автосервис Строгино</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Диагностика выхлопной системы</t>
+          <t>Чип-тюнинг</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1422,19 +1430,19 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Осмотр выпускного тракта на подъёмнике, поиск прогаров и подсосов, проверка катализатора. Актуальную стоимость уточните по телефону.</t>
+          <t>Настройка блока управления двигателем с обязательной диагностикой до работ. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Диагностика перед покупкой авто</t>
+          <t>Автосервис недорого Красногорск</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Промывка форсунок</t>
+          <t>Дефектовка перед ремонтом</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1443,19 +1451,19 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Чистка форсунок с проверкой факела распыла. Актуальную стоимость уточните по телефону.</t>
+          <t>Разбираем узел, показываем износ и называем итоговую сумму до начала работ. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Замена коллектора</t>
+          <t>Автосервис отзывы</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Замена выпускного коллектора</t>
+          <t>Замена ступицы</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1464,19 +1472,19 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Замена коллектора и прокладок, устранение течи выхлопных газов. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена ступичного узла или подшипника, проверка второй стороны. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Компьютерная диагностика автомобилей Москва</t>
+          <t>Автосервис рядом</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Компьютерная диагностика</t>
+          <t>Замена бензонасоса</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1485,19 +1493,19 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Чтение ошибок и живых данных, объясняем причину простыми словами. Актуальную стоимость уточните по телефону.</t>
+          <t>Снятие лючка или бака, замена насоса, проверка производительности. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Компьютерная диагностика автомобиля</t>
+          <t>Автосервис рядом со мной</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Диагностика перед чип-тюнингом</t>
+          <t>Переклейка поддона двигателя</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1506,19 +1514,19 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Полная компьютерная диагностика двигателя и электроники перед прошивкой. Актуальную стоимость уточните по телефону.</t>
+          <t>Снятие поддона, очистка привалочных плоскостей, герметизация. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Лучший автосервис Красногорск</t>
+          <t>Автосервис с гарантией</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Замена стоек стабилизатора</t>
+          <t>Замена опоры амортизатора</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1527,19 +1535,19 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Замена стоек и втулок стабилизатора, проверка после ремонта. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена опор и опорных подшипников, осмотр пружин и пыльников. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Откат чип-тюнинга</t>
+          <t>Автосервис улица Жуковского</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Восстановление заводской прошивки</t>
+          <t>Замена топливного фильтра</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1548,19 +1556,19 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Возврат к штатным настройкам производителя. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена фильтра тонкой очистки, проверка давления в топливной рампе. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Отключение DPF</t>
+          <t>Автосервис улица Жуковского</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Отключение сажевого фильтра DPF</t>
+          <t>Замена антифриза</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1569,19 +1577,19 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Программная настройка после удаления или при неисправности сажевого фильтра. Актуальную стоимость уточните по телефону.</t>
+          <t>Полная замена охлаждающей жидкости с промывкой системы. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Отключить EGR</t>
+          <t>Адаптация ЭБУ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Отключение EGR</t>
+          <t>Отключение ошибок и адаптация блоков управления</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1590,19 +1598,19 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Программное отключение системы рециркуляции отработавших газов. Актуальную стоимость уточните по телефону.</t>
+          <t>Настройка электронных систем и адаптация блоков после ремонта, устранение программных ошибок. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Проверенный автосервис</t>
+          <t>Диагностика ABS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Замена сайлентблоков</t>
+          <t>Диагностика и ремонт ABS</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1611,19 +1619,19 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Перепрессовка сайлентблоков рычагов, работа любой сложности. Актуальную стоимость уточните по телефону.</t>
+          <t>Проверка датчиков и блока, устранение горящей лампы ABS. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Прошивка фургона</t>
+          <t>Диагностика Авто Москва</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Чип-тюнинг коммерческого транспорта</t>
+          <t>Комплексная диагностика</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1632,19 +1640,19 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Настройка ЭБУ фургонов и коммерческих автомобилей под реальную загрузку. Актуальную стоимость уточните по телефону.</t>
+          <t>Двигатель, электрика, подвеска и тормоза по одному чек-листу. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ремонт авто Красногорск</t>
+          <t>Диагностика автомобиля Москва</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Замена водяного насоса</t>
+          <t>Замена прокладки клапанной крышки</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1653,19 +1661,19 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Снятие и установка помпы, замена прокладки, заливка антифриза. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена прокладки, устранение запотевания и течи масла. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ремонт авто Москва</t>
+          <t>Диагностика автомобиля Москва</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ремонт гофры глушителя</t>
+          <t>Промывка двигателя</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1674,19 +1682,19 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Замена или вварка гофры, восстановление герметичности выпуска. Актуальную стоимость уточните по телефону.</t>
+          <t>Мягкая промывка масляной системы при замене масла. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ремонт авто недорого</t>
+          <t>Диагностика выхлопа Москва</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Диагностика подвески</t>
+          <t>Диагностика выхлопной системы</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1695,19 +1703,19 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Осмотр подвески на подъёмнике: рычаги, стойки, шаровые, сайлентблоки. Показываем каждый люфт. Актуальную стоимость уточните по телефону.</t>
+          <t>Осмотр выпускного тракта на подъёмнике, поиск прогаров и подсосов, проверка катализатора. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ремонт авто недорого</t>
+          <t>Диагностика выхлопа Москва</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Замена натяжителя приводного ремня</t>
+          <t>Осмотр выхлопной системы на подъёмнике</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1716,19 +1724,19 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Замена натяжного механизма, проверка ремня навесного оборудования. Актуальную стоимость уточните по телефону.</t>
+          <t>Ищем прогары, подсосы и трещины, показываем всё на машине. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ремонт автомобилей рядом</t>
+          <t>Диагностика перед покупкой авто</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Замена приводного ремня</t>
+          <t>Промывка форсунок</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1737,19 +1745,19 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Замена ремня навесного оборудования, осмотр роликов. Актуальную стоимость уточните по телефону.</t>
+          <t>Чистка форсунок с проверкой факела распыла. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ремонт автомобилей рядом</t>
+          <t>Дизельный сервис Красногорск</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Замена ГРМ</t>
+          <t>Диагностика дизельного двигателя</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1758,19 +1766,19 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Замена ремня или цепи ГРМ по регламенту производителя. Актуальную стоимость уточните по телефону.</t>
+          <t>Проверка топливной аппаратуры, обратки, давления и сажевого фильтра. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ремонт двигателя Москва</t>
+          <t>Дизельный сервис Красногорск</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Замена масла в двигателе</t>
+          <t>Замена свечей накаливания</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1779,19 +1787,19 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Замена масла и фильтра, доливка жидкостей, сброс межсервисного интервала. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена свечей накала, проверка реле и проводки — уходит тяжёлый холодный пуск. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>СТО Красногорск</t>
+          <t>Замена ШРУСа</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ремонт глушителя</t>
+          <t>Замена ШРУСа и пыльника</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1800,19 +1808,19 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Устранение прогара, замена банки и резонатора, сварка аргоном. Актуальную стоимость уточните по телефону.</t>
+          <t>Хруст при повороте — меняем шарнир или пыльник, пока не рассыпалось. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Сколько стоит ремонт авто</t>
+          <t>Замена аккумулятора</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Установка защиты картера</t>
+          <t>Подбор и замена аккумулятора</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1821,19 +1829,19 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Подбор защиты под модель, установка с комплектом крепежа. Актуальную стоимость уточните по телефону.</t>
+          <t>Проверка АКБ под нагрузкой, подбор по машине, регистрация при необходимости. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Стоимость диагностики авто</t>
+          <t>Замена амортизаторов</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Чистка дроссельной заслонки</t>
+          <t>Замена амортизаторов</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1842,19 +1850,19 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Снятие и промывка заслонки, адаптация после чистки. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена стоек в паре, осмотр опор и пружин, развал-схождение после. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ТО автомобиля</t>
+          <t>Замена воздушного фильтра</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Замена свечей зажигания</t>
+          <t>Замена воздушного фильтра</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1863,19 +1871,19 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Замена свечей, проверка катушек и состояния свечных колодцев. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена фильтра, осмотр патрубков впуска на подсос. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Техническое обслуживание авто</t>
+          <t>Замена гофры глушителя</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Замена ролика приводного ремня</t>
+          <t>Замена гофры</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1884,19 +1892,19 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Замена обводных и натяжных роликов, проверка шума подшипников. Актуальную стоимость уточните по телефону.</t>
+          <t>Вырезаем прогоревшую гофру, ставим новую с проваром по кругу. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Удаление катализатора</t>
+          <t>Замена датчиков двигателя</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Отключение катализатора</t>
+          <t>Замена датчика коленвала и распредвала</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1905,19 +1913,19 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Программное отключение ошибок после удаления катализатора. Актуальную стоимость уточните по телефону.</t>
+          <t>Подбор и замена датчиков, проверка сигнала по сканеру. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Хороший автосервис Москва</t>
+          <t>Замена катализатора</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Замена поворотного кулака</t>
+          <t>Замена катализатора</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1926,19 +1934,19 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Замена кулака с последующей регулировкой развала-схождения. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена на новый катализатор или на пламегаситель — на выбор, с прошивкой. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Чип-тюнинг Евро-2</t>
+          <t>Замена коллектора</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Прошивка Евро-2</t>
+          <t>Замена выпускного коллектора</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1947,19 +1955,19 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Программная адаптация автомобиля под экологический стандарт Евро-2. Актуальную стоимость уточните по телефону.</t>
+          <t>Замена коллектора и прокладок, устранение течи выхлопных газов. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Чип-тюнинг Москва</t>
+          <t>Замена ламп</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Чип-тюнинг бензинового автомобиля</t>
+          <t>Замена ламп головного света</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1968,19 +1976,19 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Настройка ЭБУ бензинового двигателя: динамика, отклик педали, ровная работа. Актуальную стоимость уточните по телефону.</t>
+          <t>Подбор и установка ламп, проверка проводки и разъёмов. Актуальную стоимость уточните по телефону.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Чип-тюнинг дизель</t>
+          <t>Замена лямбда-зонда</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Чип-тюнинг дизельного автомобиля</t>
+          <t>Замена датчика кислорода (лямбда-зонда)</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1988,6 +1996,1392 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
+        <is>
+          <t>Подбор и замена лямбда-зонда, проверка показаний по сканеру. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Замена масла в МКПП</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Замена масла в механической коробке</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Замена трансмиссионного масла, осмотр сальников. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Замена пружин подвески</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Замена пружин</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Замена просевших или лопнувших пружин, проверка отбойников. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Замена радиатора</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Замена радиатора охлаждения</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Замена радиатора и патрубков, заливка антифриза, проверка на утечки. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Замена резонатора</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Замена резонатора</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Замена среднего элемента выхлопа, подгонка по месту. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Замена ремня генератора</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Замена ремня навесного оборудования</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Замена ремня, роликов и натяжителя — уходит свист при пуске. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Замена рулевых наконечников</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Замена рулевых наконечников и тяг</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Устраняем люфт руля, после работ делаем развал-схождение. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Замена рычагов подвески</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Замена рычагов</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Замена рычагов в сборе или перепрессовка сайлентблоков. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Замена салонного фильтра</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Замена салонного фильтра</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Замена фильтра и обработка испарителя — уходит запах из печки. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Замена сальников двигателя</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Замена сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Устраняем течь масла, проверяем сапун и давление картерных газов. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Замена ступичного подшипника</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Замена ступичного подшипника</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Уходит гул на скорости. Меняем подшипник или ступицу в сборе. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Замена тормозной жидкости</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Замена тормозной жидкости с прокачкой</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Полная замена по всем контурам, проверка педали. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Замена тормозных дисков</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Замена тормозных дисков</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Замена дисков в паре, обслуживание суппортов и направляющих. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Замена цепи ГРМ</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Замена цепи ГРМ</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Замена цепи с натяжителем и успокоителями по регламенту. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Замена шаровых опор</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Замена шаровой опоры</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Замена шаровых, проверка пыльников и рычагов. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Замер противодавления</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Замер противодавления выхлопа</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Точная проверка, забит катализатор или нет, до того как что-то резать. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Компьютерная диагностика автомобилей Москва</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Компьютерная диагностика</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Чтение ошибок и живых данных, объясняем причину простыми словами. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Компьютерная диагностика автомобиля</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Диагностика перед чип-тюнингом</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Полная компьютерная диагностика двигателя и электроники перед прошивкой. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Крепления глушителя</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Замена подвесов и хомутов глушителя</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Меняем порванные резинки и хомуты — уходит стук и провисание трубы. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Лучший автосервис Красногорск</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Замена стоек стабилизатора</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Замена стоек и втулок стабилизатора, проверка после ремонта. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Обманка лямбда-зонда</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Установка обманки лямбда-зонда</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Механическая или программная обманка после удаления катализатора. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Откат чип-тюнинга</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Восстановление заводской прошивки</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Возврат к штатным настройкам производителя. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Отключение DPF</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Отключение сажевого фильтра DPF</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Программная настройка после удаления или при неисправности сажевого фильтра. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Отключение SCR</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Отключение системы SCR</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Настройка блока после отказа катализатора SCR на дизеле. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Отключение ошибок двигателя</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Устранение ошибки Check Engine</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Находим настоящую причину, а не гасим лампу. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Отключить EGR</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Отключение EGR</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Программное отключение системы рециркуляции отработавших газов. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Пламегаситель</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Установка пламегасителя</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Пламегаситель вместо изношенного катализатора: без ошибок и без потери тяги. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Пламегаситель</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Замена пламегасителя</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Меняем прогоревший пламегаситель, восстанавливаем герметичность тракта. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Поиск утечки тока</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Поиск утечки тока</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Ищем, что разряжает аккумулятор за ночь. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Проверенный автосервис</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Замена сайлентблоков</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Перепрессовка сайлентблоков рычагов, работа любой сложности. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Проверка генератора</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Диагностика зарядки и генератора</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Замер тока зарядки, проверка щёток, реле-регулятора и ремня. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Прогар выпускного коллектора</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ремонт прогара выпускного коллектора</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Снятие, проверка плоскости, замена прокладок и шпилек. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Промывка сажевого фильтра</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Промывка сажевого фильтра DPF</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Химическая промывка без снятия или со снятием — по состоянию фильтра. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Промывка системы охлаждения</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Промывка системы охлаждения</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Удаляем отложения, из-за которых машина греется в пробках. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Прошивка фургона</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг коммерческого транспорта</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Настройка ЭБУ фургонов и коммерческих автомобилей под реальную загрузку. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Прямоток</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Установка прямоточной выхлопной системы</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Подбираем звук под пожелания и варим по месту, без дребезга и прогаров. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Регулировка фар</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Регулировка света фар</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Настройка на стенде, чтобы не слепить встречных и видеть дорогу. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ремонт авто Красногорск</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Замена водяного насоса</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Снятие и установка помпы, замена прокладки, заливка антифриза. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ремонт авто Москва</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ремонт гофры глушителя</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Замена или вварка гофры, восстановление герметичности выпуска. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Ремонт авто недорого</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Диагностика подвески</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Осмотр подвески на подъёмнике: рычаги, стойки, шаровые, сайлентблоки. Показываем каждый люфт. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ремонт авто недорого</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Замена натяжителя приводного ремня</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Замена натяжного механизма, проверка ремня навесного оборудования. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Ремонт автомобилей рядом</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Замена приводного ремня</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Замена ремня навесного оборудования, осмотр роликов. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Ремонт автомобилей рядом</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Замена ГРМ</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Замена ремня или цепи ГРМ по регламенту производителя. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ремонт глушителя Красногорск</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ремонт глушителя</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Устраняем прогар и посторонний гул, варим аргоном, при необходимости меняем банку. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Ремонт глушителя Красногорск</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Замена глушителя в сборе</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Подбор и установка нового глушителя под вашу модель. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Ремонт двигателя Москва</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Замена масла в двигателе</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Замена масла и фильтра, доливка жидкостей, сброс межсервисного интервала. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Ремонт суппортов</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Обслуживание тормозных суппортов</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Чистка, смазка направляющих, замена пыльников и поршней. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>СТО Красногорск</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ремонт глушителя</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Устранение прогара, замена банки и резонатора, сварка аргоном. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>СТО рядом со мной</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Плановое техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Масло, фильтры, осмотр по 30 пунктам, отметка в сервисной книжке. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Сварка выхлопной системы</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Сварка выхлопа аргоном</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Аргонная сварка нержавейки — шов держится, а не рассыпается через сезон. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Сезонное обслуживание</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Подготовка автомобиля к зиме</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Аккумулятор, свечи, антифриз, щётки, печка — одним заездом. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Сезонное обслуживание</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Подготовка автомобиля к лету</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Кондиционер, охлаждение, тормоза, салонный фильтр. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Сколько стоит ремонт авто</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Установка защиты картера</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Подбор защиты под модель, установка с комплектом крепежа. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Стоимость диагностики авто</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Чистка дроссельной заслонки</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Снятие и промывка заслонки, адаптация после чистки. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Стронгер</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Установка стронгера</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Спортивный катколлектор-стронгер: звук тише, чем на прямотоке, ошибок нет. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ТО автомобиля</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Замена свечей зажигания</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Замена свечей, проверка катушек и состояния свечных колодцев. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Теплозащита выхлопа</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ремонт и замена теплозащитных экранов</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Убираем дребезг от прогоревших экранов над выхлопом. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Техническое обслуживание авто</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Замена ролика приводного ремня</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Замена обводных и натяжных роликов, проверка шума подшипников. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Удаление AdBlue</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Отключение системы AdBlue</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Программное отключение мочевины, снятие ограничений по мощности и запуску. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Удаление катализатора</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Отключение катализатора</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Программное отключение ошибок после удаления катализатора. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Удаление катализатора Красногорск</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Удаление катализатора с прошивкой</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Механическое удаление и корректная программная настройка, чтобы не горел Check. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Удаление сажевого фильтра</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Удаление DPF с прошивкой</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Механическое удаление и настройка блока управления под работу без сажевого. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Хороший автосервис Москва</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Замена поворотного кулака</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Замена кулака с последующей регулировкой развала-схождения. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг Евро-2</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Прошивка Евро-2</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Программная адаптация автомобиля под экологический стандарт Евро-2. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг Красногорск</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг с диагностикой</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Диагностика, снятие заводской прошивки, настройка и проверка на выходе. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг Москва</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг бензинового автомобиля</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Настройка ЭБУ бензинового двигателя: динамика, отклик педали, ровная работа. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг дизель</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг дизельного автомобиля</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
         <is>
           <t>Оптимизация работы дизеля: тяга и расход при спокойной езде. Актуальную стоимость уточните по телефону.</t>
         </is>
